--- a/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/Desktop 20260424075557.xlsx
+++ b/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/Desktop 20260424075557.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emma\Desktop\evidence\FileSystem\metadata\Parsed Metadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emma/DFIR-Simulation-Platform/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72415E57-018E-4E63-855E-E5598783B0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF5A9DF-53A2-0F40-89B8-B1A2BBD36DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10044" yWindow="0" windowWidth="13092" windowHeight="12336" xr2:uid="{9E0700ED-ADE3-4006-B0EA-ED5EC615322C}"/>
+    <workbookView xWindow="1820" yWindow="500" windowWidth="21320" windowHeight="12580" xr2:uid="{9E0700ED-ADE3-4006-B0EA-ED5EC615322C}"/>
   </bookViews>
   <sheets>
     <sheet name="Desktop 20260424075557" sheetId="1" r:id="rId1"/>
@@ -615,6 +615,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97DF55AE-F16F-4249-8D3F-42F47BA93338}" name="Table1" displayName="Table1" ref="A1:H4" totalsRowShown="0">
+  <autoFilter ref="A1:H4" xr:uid="{97DF55AE-F16F-4249-8D3F-42F47BA93338}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{64A1B5D5-A565-E84F-BFC5-AF4ED04EE7D6}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{FBA32D9F-D764-BB42-98F2-641A9340D892}" name="Modified Time"/>
+    <tableColumn id="3" xr3:uid="{A94DD963-64DE-9A47-B52D-6F00F555FE3E}" name="Change Time"/>
+    <tableColumn id="4" xr3:uid="{7741F180-35AD-8D44-817A-5686541FCE58}" name="Access Time"/>
+    <tableColumn id="5" xr3:uid="{C947310F-F12E-EF4B-A3E5-F94122194144}" name="Created Time"/>
+    <tableColumn id="6" xr3:uid="{420AA698-64F0-2B49-95BC-C052BEA0E807}" name="Size"/>
+    <tableColumn id="7" xr3:uid="{6F6B3222-FEB0-3845-AD4C-184A0742833B}" name="Location"/>
+    <tableColumn id="8" xr3:uid="{09E961CA-0824-8244-9F3F-5E30A7963538}" name="Extension"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -935,16 +952,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B2B4F4-FA89-4296-BFB1-4B05E8A26268}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="45" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -970,7 +987,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -996,7 +1013,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1022,7 +1039,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1050,5 +1067,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>